--- a/tests/data/isotope_benchmark.xlsx
+++ b/tests/data/isotope_benchmark.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="38">
   <si>
     <t>算法</t>
   </si>
@@ -37,6 +37,15 @@
     <t>t_Model</t>
   </si>
   <si>
+    <t>t_Albarede</t>
+  </si>
+  <si>
+    <t>mu_Albarede</t>
+  </si>
+  <si>
+    <t>kappa_Albarede</t>
+  </si>
+  <si>
     <t>Reference</t>
   </si>
   <si>
@@ -58,6 +67,9 @@
     <t>Maltese &amp; Mezger (2020)</t>
   </si>
   <si>
+    <t>Albarède &amp; Juteau (1984)</t>
+  </si>
+  <si>
     <t>朱炳泉. (2001). 地球化学省与地球化学急变带. 科学出版社. 23页</t>
   </si>
   <si>
@@ -65,6 +77,57 @@
   </si>
   <si>
     <t>Armistead, S., Eglington, B., &amp; Pehrsson, S. (2023). PbIso: An R package and web app for calculating and plotting Pb isotope data. Earth Sciences. https://doi.org/10.31223/X56G84</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Johansson, 1984</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Johansson, 1983</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Yener et al., 1991</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Köppel, 1997 see Marcoux</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Stos-Gale et al., 1996</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: 30</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: http://brettscaife.net/lead/data/index.html</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: NHG/SSG</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Milot_CG_2021</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Heredia (unpublished)</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Baron et al., 2006</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Rohl, 1996</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Guénette-Beck, 2005</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Valera et al., 2005</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Marcoux, 1986</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Vaasjoki et al., 1999</t>
+  </si>
+  <si>
+    <t>Pb_BDB galena DB (SilverQuest_v1); AJ84 pipeline. 原始来源: Vaasjoki, 1981</t>
   </si>
 </sst>
 </file>
@@ -422,10 +485,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -450,10 +513,19 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>18.252</v>
@@ -470,13 +542,13 @@
       <c r="F2">
         <v>38.76</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>18.103</v>
@@ -493,13 +565,13 @@
       <c r="F3">
         <v>33.15</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>18.073</v>
@@ -516,13 +588,13 @@
       <c r="F4">
         <v>33.01</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>18.15</v>
@@ -539,13 +611,13 @@
       <c r="F5">
         <v>33.32</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>18.096</v>
@@ -562,13 +634,13 @@
       <c r="F6">
         <v>32.94</v>
       </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="K6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>18.276</v>
@@ -585,13 +657,13 @@
       <c r="F7">
         <v>39.79</v>
       </c>
-      <c r="H7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="K7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>18.165</v>
@@ -608,13 +680,13 @@
       <c r="F8">
         <v>35.13</v>
       </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="K8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>18</v>
@@ -631,13 +703,13 @@
       <c r="F9">
         <v>26.88</v>
       </c>
-      <c r="H9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="K9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>18.268</v>
@@ -654,13 +726,13 @@
       <c r="F10">
         <v>37.89</v>
       </c>
-      <c r="H10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="K10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>18.363</v>
@@ -677,13 +749,13 @@
       <c r="F11">
         <v>43.78</v>
       </c>
-      <c r="H11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="K11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B12">
         <v>18.385</v>
@@ -700,13 +772,13 @@
       <c r="F12">
         <v>42.36</v>
       </c>
-      <c r="H12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="K12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <v>18.159</v>
@@ -723,13 +795,13 @@
       <c r="F13">
         <v>37.06</v>
       </c>
-      <c r="H13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="K13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B14">
         <v>18.165</v>
@@ -746,13 +818,13 @@
       <c r="F14">
         <v>38.29</v>
       </c>
-      <c r="H14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="K14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>18.354</v>
@@ -769,13 +841,13 @@
       <c r="F15">
         <v>43.65</v>
       </c>
-      <c r="H15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="K15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>18.003</v>
@@ -792,13 +864,13 @@
       <c r="F16">
         <v>25.49</v>
       </c>
-      <c r="H16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="K16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B17">
         <v>18.341</v>
@@ -815,13 +887,13 @@
       <c r="F17">
         <v>42.98</v>
       </c>
-      <c r="H17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="K17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B18">
         <v>18.341</v>
@@ -838,13 +910,13 @@
       <c r="F18">
         <v>42.99</v>
       </c>
-      <c r="H18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="K18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B19">
         <v>18.503</v>
@@ -861,13 +933,13 @@
       <c r="F19">
         <v>48.44</v>
       </c>
-      <c r="H19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="K19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B20">
         <v>18.489</v>
@@ -884,13 +956,13 @@
       <c r="F20">
         <v>47.81</v>
       </c>
-      <c r="H20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="K20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B21">
         <v>18.404</v>
@@ -907,13 +979,13 @@
       <c r="F21">
         <v>43.12</v>
       </c>
-      <c r="H21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="K21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B22">
         <v>18.367</v>
@@ -930,13 +1002,13 @@
       <c r="F22">
         <v>38.38</v>
       </c>
-      <c r="H22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="K22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B23">
         <v>18.62</v>
@@ -953,13 +1025,13 @@
       <c r="F23">
         <v>52.65</v>
       </c>
-      <c r="H23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="K23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B24">
         <v>18.512</v>
@@ -976,13 +1048,13 @@
       <c r="F24">
         <v>47.07</v>
       </c>
-      <c r="H24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="K24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B25">
         <v>18.356</v>
@@ -999,13 +1071,13 @@
       <c r="F25">
         <v>42.81</v>
       </c>
-      <c r="H25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="K25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B26">
         <v>18.471</v>
@@ -1022,13 +1094,13 @@
       <c r="F26">
         <v>46.32</v>
       </c>
-      <c r="H26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="K26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B27">
         <v>18.562</v>
@@ -1045,13 +1117,13 @@
       <c r="F27">
         <v>51.53</v>
       </c>
-      <c r="H27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="K27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B28">
         <v>18.417</v>
@@ -1068,13 +1140,13 @@
       <c r="F28">
         <v>45.4</v>
       </c>
-      <c r="H28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="K28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B29">
         <v>18.402</v>
@@ -1091,13 +1163,13 @@
       <c r="F29">
         <v>42.13</v>
       </c>
-      <c r="H29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="K29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B30">
         <v>18.185</v>
@@ -1114,13 +1186,13 @@
       <c r="F30">
         <v>34.38</v>
       </c>
-      <c r="H30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="K30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B31">
         <v>18.212</v>
@@ -1137,13 +1209,13 @@
       <c r="F31">
         <v>51.66</v>
       </c>
-      <c r="H31" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="K31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B32">
         <v>18.61</v>
@@ -1160,13 +1232,13 @@
       <c r="F32">
         <v>51.6</v>
       </c>
-      <c r="H32" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="K32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B33">
         <v>18.441</v>
@@ -1183,13 +1255,13 @@
       <c r="F33">
         <v>46.29</v>
       </c>
-      <c r="H33" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="K33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B34">
         <v>18.457</v>
@@ -1206,13 +1278,13 @@
       <c r="F34">
         <v>45.83</v>
       </c>
-      <c r="H34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="K34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B35">
         <v>18.566</v>
@@ -1229,13 +1301,13 @@
       <c r="F35">
         <v>51.35</v>
       </c>
-      <c r="H35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="K35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B36">
         <v>18.61</v>
@@ -1252,13 +1324,13 @@
       <c r="F36">
         <v>51.53</v>
       </c>
-      <c r="H36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="K36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B37">
         <v>16.589</v>
@@ -1275,13 +1347,13 @@
       <c r="F37">
         <v>29.3</v>
       </c>
-      <c r="H37" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="K37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B38">
         <v>16.927</v>
@@ -1298,13 +1370,13 @@
       <c r="F38">
         <v>31.44</v>
       </c>
-      <c r="H38" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+      <c r="K38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B39">
         <v>16.974</v>
@@ -1321,13 +1393,13 @@
       <c r="F39">
         <v>31.77</v>
       </c>
-      <c r="H39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+      <c r="K39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B40">
         <v>17.029</v>
@@ -1344,13 +1416,13 @@
       <c r="F40">
         <v>32.66</v>
       </c>
-      <c r="H40" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+      <c r="K40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B41">
         <v>17.038</v>
@@ -1367,13 +1439,13 @@
       <c r="F41">
         <v>30.89</v>
       </c>
-      <c r="H41" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+      <c r="K41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B42">
         <v>17.062</v>
@@ -1390,13 +1462,13 @@
       <c r="F42">
         <v>31.29</v>
       </c>
-      <c r="H42" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+      <c r="K42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B43">
         <v>17.38</v>
@@ -1413,13 +1485,13 @@
       <c r="F43">
         <v>49.48</v>
       </c>
-      <c r="H43" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="K43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B44">
         <v>17.421</v>
@@ -1436,13 +1508,13 @@
       <c r="F44">
         <v>35.57</v>
       </c>
-      <c r="H44" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+      <c r="K44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B45">
         <v>17.434</v>
@@ -1459,13 +1531,13 @@
       <c r="F45">
         <v>35.16</v>
       </c>
-      <c r="H45" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+      <c r="K45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B46">
         <v>17.438</v>
@@ -1482,13 +1554,13 @@
       <c r="F46">
         <v>39.93</v>
       </c>
-      <c r="H46" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+      <c r="K46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B47">
         <v>16.951</v>
@@ -1505,13 +1577,13 @@
       <c r="F47">
         <v>30.16</v>
       </c>
-      <c r="H47" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+      <c r="K47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B48">
         <v>16.744</v>
@@ -1528,13 +1600,13 @@
       <c r="F48">
         <v>28.6</v>
       </c>
-      <c r="H48" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="K48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B49">
         <v>22.099</v>
@@ -1551,13 +1623,13 @@
       <c r="F49">
         <v>193.54</v>
       </c>
-      <c r="H49" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="K49" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B50">
         <v>23.262</v>
@@ -1574,13 +1646,13 @@
       <c r="F50">
         <v>239.55</v>
       </c>
-      <c r="H50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="K50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B51">
         <v>23.323</v>
@@ -1597,13 +1669,13 @@
       <c r="F51">
         <v>242.56</v>
       </c>
-      <c r="H51" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+      <c r="K51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B52">
         <v>22.023</v>
@@ -1620,13 +1692,13 @@
       <c r="F52">
         <v>191.24</v>
       </c>
-      <c r="H52" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+      <c r="K52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B53">
         <v>22.149</v>
@@ -1643,13 +1715,13 @@
       <c r="F53">
         <v>195.77</v>
       </c>
-      <c r="H53" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+      <c r="K53" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B54">
         <v>22.624</v>
@@ -1666,13 +1738,13 @@
       <c r="F54">
         <v>208.24</v>
       </c>
-      <c r="H54" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+      <c r="K54" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B55">
         <v>15.359</v>
@@ -1686,13 +1758,13 @@
       <c r="G55">
         <v>1466</v>
       </c>
-      <c r="H55" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+      <c r="K55" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B56">
         <v>15.427</v>
@@ -1706,13 +1778,13 @@
       <c r="G56">
         <v>1422</v>
       </c>
-      <c r="H56" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+      <c r="K56" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B57">
         <v>15.459</v>
@@ -1726,13 +1798,13 @@
       <c r="G57">
         <v>1355</v>
       </c>
-      <c r="H57" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+      <c r="K57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B58">
         <v>19.086</v>
@@ -1746,13 +1818,13 @@
       <c r="G58">
         <v>-1044</v>
       </c>
-      <c r="H58" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+      <c r="K58" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B59">
         <v>14.208</v>
@@ -1766,13 +1838,13 @@
       <c r="G59">
         <v>2394</v>
       </c>
-      <c r="H59" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+      <c r="K59" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B60">
         <v>13.318</v>
@@ -1786,13 +1858,13 @@
       <c r="G60">
         <v>2587</v>
       </c>
-      <c r="H60" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+      <c r="K60" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B61">
         <v>15.359</v>
@@ -1806,13 +1878,13 @@
       <c r="G61">
         <v>1750</v>
       </c>
-      <c r="H61" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+      <c r="K61" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B62">
         <v>15.427</v>
@@ -1826,13 +1898,13 @@
       <c r="G62">
         <v>1709</v>
       </c>
-      <c r="H62" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+      <c r="K62" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B63">
         <v>15.459</v>
@@ -1846,13 +1918,13 @@
       <c r="G63">
         <v>1612</v>
       </c>
-      <c r="H63" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+      <c r="K63" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B64">
         <v>19.086</v>
@@ -1866,13 +1938,13 @@
       <c r="G64">
         <v>-176</v>
       </c>
-      <c r="H64" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+      <c r="K64" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B65">
         <v>14.208</v>
@@ -1886,13 +1958,13 @@
       <c r="G65">
         <v>2797</v>
       </c>
-      <c r="H65" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+      <c r="K65" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B66">
         <v>13.318</v>
@@ -1906,13 +1978,13 @@
       <c r="G66">
         <v>2701</v>
       </c>
-      <c r="H66" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+      <c r="K66" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B67">
         <v>15.359</v>
@@ -1926,13 +1998,13 @@
       <c r="G67">
         <v>1648</v>
       </c>
-      <c r="H67" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+      <c r="K67" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B68">
         <v>15.427</v>
@@ -1946,13 +2018,13 @@
       <c r="G68">
         <v>1606</v>
       </c>
-      <c r="H68" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+      <c r="K68" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B69">
         <v>15.459</v>
@@ -1966,13 +2038,13 @@
       <c r="G69">
         <v>1543</v>
       </c>
-      <c r="H69" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+      <c r="K69" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B70">
         <v>19.086</v>
@@ -1986,13 +2058,13 @@
       <c r="G70">
         <v>-660</v>
       </c>
-      <c r="H70" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
+      <c r="K70" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B71">
         <v>14.208</v>
@@ -2006,13 +2078,13 @@
       <c r="G71">
         <v>2526</v>
       </c>
-      <c r="H71" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
+      <c r="K71" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B72">
         <v>13.318</v>
@@ -2026,13 +2098,13 @@
       <c r="G72">
         <v>2711</v>
       </c>
-      <c r="H72" t="s">
+      <c r="K72" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" t="s">
-        <v>13</v>
       </c>
       <c r="B73">
         <v>15.359</v>
@@ -2046,13 +2118,13 @@
       <c r="G73">
         <v>1629</v>
       </c>
-      <c r="H73" t="s">
+      <c r="K73" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" t="s">
-        <v>13</v>
       </c>
       <c r="B74">
         <v>15.427</v>
@@ -2066,13 +2138,13 @@
       <c r="G74">
         <v>1587</v>
       </c>
-      <c r="H74" t="s">
+      <c r="K74" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" t="s">
-        <v>13</v>
       </c>
       <c r="B75">
         <v>15.459</v>
@@ -2086,13 +2158,13 @@
       <c r="G75">
         <v>1523</v>
       </c>
-      <c r="H75" t="s">
+      <c r="K75" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" t="s">
-        <v>13</v>
       </c>
       <c r="B76">
         <v>19.086</v>
@@ -2106,13 +2178,13 @@
       <c r="G76">
         <v>-693</v>
       </c>
-      <c r="H76" t="s">
+      <c r="K76" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" t="s">
-        <v>13</v>
       </c>
       <c r="B77">
         <v>14.208</v>
@@ -2126,13 +2198,13 @@
       <c r="G77">
         <v>2516</v>
       </c>
-      <c r="H77" t="s">
+      <c r="K77" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" t="s">
-        <v>13</v>
       </c>
       <c r="B78">
         <v>13.318</v>
@@ -2146,8 +2218,528 @@
       <c r="G78">
         <v>2697</v>
       </c>
-      <c r="H78" t="s">
-        <v>16</v>
+      <c r="K78" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" t="s">
+        <v>17</v>
+      </c>
+      <c r="B79">
+        <v>36.91</v>
+      </c>
+      <c r="C79">
+        <v>17.847</v>
+      </c>
+      <c r="D79">
+        <v>52.47</v>
+      </c>
+      <c r="H79">
+        <v>-8980</v>
+      </c>
+      <c r="I79">
+        <v>16.67</v>
+      </c>
+      <c r="J79">
+        <v>2.2733</v>
+      </c>
+      <c r="K79" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" t="s">
+        <v>17</v>
+      </c>
+      <c r="B80">
+        <v>36.883</v>
+      </c>
+      <c r="C80">
+        <v>17.843</v>
+      </c>
+      <c r="D80">
+        <v>52.306</v>
+      </c>
+      <c r="H80">
+        <v>-8969.6</v>
+      </c>
+      <c r="I80">
+        <v>16.657</v>
+      </c>
+      <c r="J80">
+        <v>2.259</v>
+      </c>
+      <c r="K80" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" t="s">
+        <v>17</v>
+      </c>
+      <c r="B81">
+        <v>19.936</v>
+      </c>
+      <c r="C81">
+        <v>15.75</v>
+      </c>
+      <c r="D81">
+        <v>38.39</v>
+      </c>
+      <c r="H81">
+        <v>-651.02</v>
+      </c>
+      <c r="I81">
+        <v>9.947100000000001</v>
+      </c>
+      <c r="J81">
+        <v>3.0987</v>
+      </c>
+      <c r="K81" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" t="s">
+        <v>17</v>
+      </c>
+      <c r="B82">
+        <v>18.988</v>
+      </c>
+      <c r="C82">
+        <v>15.709</v>
+      </c>
+      <c r="D82">
+        <v>39.081</v>
+      </c>
+      <c r="H82">
+        <v>-19.148</v>
+      </c>
+      <c r="I82">
+        <v>9.919700000000001</v>
+      </c>
+      <c r="J82">
+        <v>3.9024</v>
+      </c>
+      <c r="K82" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B83">
+        <v>19.002</v>
+      </c>
+      <c r="C83">
+        <v>15.718</v>
+      </c>
+      <c r="D83">
+        <v>38.85</v>
+      </c>
+      <c r="H83">
+        <v>-11.564</v>
+      </c>
+      <c r="I83">
+        <v>9.951599999999999</v>
+      </c>
+      <c r="J83">
+        <v>3.785</v>
+      </c>
+      <c r="K83" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" t="s">
+        <v>17</v>
+      </c>
+      <c r="B84">
+        <v>18.94</v>
+      </c>
+      <c r="C84">
+        <v>15.6980402</v>
+      </c>
+      <c r="D84">
+        <v>39.0133696</v>
+      </c>
+      <c r="H84">
+        <v>-5.3928</v>
+      </c>
+      <c r="I84">
+        <v>9.8863</v>
+      </c>
+      <c r="J84">
+        <v>3.8954</v>
+      </c>
+      <c r="K84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" t="s">
+        <v>17</v>
+      </c>
+      <c r="B85">
+        <v>18.75</v>
+      </c>
+      <c r="C85">
+        <v>15.639</v>
+      </c>
+      <c r="D85">
+        <v>38.738</v>
+      </c>
+      <c r="H85">
+        <v>18.349</v>
+      </c>
+      <c r="I85">
+        <v>9.6944</v>
+      </c>
+      <c r="J85">
+        <v>3.8572</v>
+      </c>
+      <c r="K85" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" t="s">
+        <v>17</v>
+      </c>
+      <c r="B86">
+        <v>18.851</v>
+      </c>
+      <c r="C86">
+        <v>15.688</v>
+      </c>
+      <c r="D86">
+        <v>38.94</v>
+      </c>
+      <c r="H86">
+        <v>40.829</v>
+      </c>
+      <c r="I86">
+        <v>9.863799999999999</v>
+      </c>
+      <c r="J86">
+        <v>3.9116</v>
+      </c>
+      <c r="K86" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" t="s">
+        <v>17</v>
+      </c>
+      <c r="B87">
+        <v>18.86</v>
+      </c>
+      <c r="C87">
+        <v>15.694</v>
+      </c>
+      <c r="D87">
+        <v>38.946</v>
+      </c>
+      <c r="H87">
+        <v>46.027</v>
+      </c>
+      <c r="I87">
+        <v>9.885199999999999</v>
+      </c>
+      <c r="J87">
+        <v>3.911</v>
+      </c>
+      <c r="K87" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" t="s">
+        <v>17</v>
+      </c>
+      <c r="B88">
+        <v>18.75</v>
+      </c>
+      <c r="C88">
+        <v>15.6849375</v>
+      </c>
+      <c r="D88">
+        <v>38.97</v>
+      </c>
+      <c r="H88">
+        <v>109.77</v>
+      </c>
+      <c r="I88">
+        <v>9.8711</v>
+      </c>
+      <c r="J88">
+        <v>3.9902</v>
+      </c>
+      <c r="K88" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" t="s">
+        <v>17</v>
+      </c>
+      <c r="B89">
+        <v>18.74991</v>
+      </c>
+      <c r="C89">
+        <v>15.68492</v>
+      </c>
+      <c r="D89">
+        <v>39.00951</v>
+      </c>
+      <c r="H89">
+        <v>110</v>
+      </c>
+      <c r="I89">
+        <v>9.871</v>
+      </c>
+      <c r="J89">
+        <v>4.01</v>
+      </c>
+      <c r="K89" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" t="s">
+        <v>17</v>
+      </c>
+      <c r="B90">
+        <v>18.608378387</v>
+      </c>
+      <c r="C90">
+        <v>15.654317981</v>
+      </c>
+      <c r="D90">
+        <v>38.6682589138</v>
+      </c>
+      <c r="H90">
+        <v>155.2683947134</v>
+      </c>
+      <c r="I90">
+        <v>9.7805578178</v>
+      </c>
+      <c r="J90">
+        <v>3.9180512297</v>
+      </c>
+      <c r="K90" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" t="s">
+        <v>17</v>
+      </c>
+      <c r="B91">
+        <v>18.472</v>
+      </c>
+      <c r="C91">
+        <v>15.668</v>
+      </c>
+      <c r="D91">
+        <v>38.677</v>
+      </c>
+      <c r="H91">
+        <v>282.39</v>
+      </c>
+      <c r="I91">
+        <v>9.863899999999999</v>
+      </c>
+      <c r="J91">
+        <v>4.0177</v>
+      </c>
+      <c r="K91" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" t="s">
+        <v>17</v>
+      </c>
+      <c r="B92">
+        <v>18.384</v>
+      </c>
+      <c r="C92">
+        <v>15.64092336</v>
+      </c>
+      <c r="D92">
+        <v>38.41391952</v>
+      </c>
+      <c r="H92">
+        <v>296.33</v>
+      </c>
+      <c r="I92">
+        <v>9.776999999999999</v>
+      </c>
+      <c r="J92">
+        <v>3.9281</v>
+      </c>
+      <c r="K92" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93">
+        <v>18.449</v>
+      </c>
+      <c r="C93">
+        <v>15.667</v>
+      </c>
+      <c r="D93">
+        <v>38.549</v>
+      </c>
+      <c r="H93">
+        <v>297.42</v>
+      </c>
+      <c r="I93">
+        <v>9.8652</v>
+      </c>
+      <c r="J93">
+        <v>3.9653</v>
+      </c>
+      <c r="K93" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" t="s">
+        <v>17</v>
+      </c>
+      <c r="B94">
+        <v>18.4501845018</v>
+      </c>
+      <c r="C94">
+        <v>15.8487084871</v>
+      </c>
+      <c r="D94">
+        <v>38.9298892989</v>
+      </c>
+      <c r="H94">
+        <v>613.41</v>
+      </c>
+      <c r="I94">
+        <v>10.605</v>
+      </c>
+      <c r="J94">
+        <v>4.2278</v>
+      </c>
+      <c r="K94" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" t="s">
+        <v>17</v>
+      </c>
+      <c r="B95">
+        <v>17.587</v>
+      </c>
+      <c r="C95">
+        <v>15.542</v>
+      </c>
+      <c r="D95">
+        <v>37.638</v>
+      </c>
+      <c r="H95">
+        <v>708.7</v>
+      </c>
+      <c r="I95">
+        <v>9.601100000000001</v>
+      </c>
+      <c r="J95">
+        <v>4.0166</v>
+      </c>
+      <c r="K95" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" t="s">
+        <v>17</v>
+      </c>
+      <c r="B96">
+        <v>13.398</v>
+      </c>
+      <c r="C96">
+        <v>14.659</v>
+      </c>
+      <c r="D96">
+        <v>33.15</v>
+      </c>
+      <c r="H96">
+        <v>3013</v>
+      </c>
+      <c r="I96">
+        <v>11.608</v>
+      </c>
+      <c r="J96">
+        <v>3.9486</v>
+      </c>
+      <c r="K96" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" t="s">
+        <v>17</v>
+      </c>
+      <c r="B97">
+        <v>13.6</v>
+      </c>
+      <c r="C97">
+        <v>14.863</v>
+      </c>
+      <c r="D97">
+        <v>33.44</v>
+      </c>
+      <c r="H97">
+        <v>3070.6</v>
+      </c>
+      <c r="I97">
+        <v>13.516</v>
+      </c>
+      <c r="J97">
+        <v>4.1551</v>
+      </c>
+      <c r="K97" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" t="s">
+        <v>17</v>
+      </c>
+      <c r="B98">
+        <v>13.606</v>
+      </c>
+      <c r="C98">
+        <v>14.879</v>
+      </c>
+      <c r="D98">
+        <v>33.494</v>
+      </c>
+      <c r="H98">
+        <v>3085.1</v>
+      </c>
+      <c r="I98">
+        <v>13.808</v>
+      </c>
+      <c r="J98">
+        <v>4.2419</v>
+      </c>
+      <c r="K98" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
